--- a/master-db/mini.xlsx
+++ b/master-db/mini.xlsx
@@ -64,7 +64,7 @@
     <t/>
   </si>
   <si>
-    <t>대기</t>
+    <t>완료</t>
   </si>
   <si>
     <t>쿠퍼 S 4세대</t>
